--- a/BD_RRHH.xlsx
+++ b/BD_RRHH.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Recursos" sheetId="1" r:id="rId1"/>
+    <sheet name="Recursos_MO" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,14 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E10"/>
-  <cols>
-    <col min="1" max="1" width="10.83203125" customWidth="1"/>
-    <col min="2" max="2" width="40.83203125" customWidth="1"/>
-    <col min="3" max="3" width="15.83203125" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:E6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -445,7 +438,7 @@
         <v>LH-OPE</v>
       </c>
       <c r="B3" t="str">
-        <v>Operario Civil</v>
+        <v>Operario de Obra Civil</v>
       </c>
       <c r="C3" t="str">
         <v>mano_obra</v>
@@ -462,7 +455,7 @@
         <v>LH-OFI</v>
       </c>
       <c r="B4" t="str">
-        <v>Oficial Carpintero/Fierrero</v>
+        <v>Oficial de Obra Civil</v>
       </c>
       <c r="C4" t="str">
         <v>mano_obra</v>
@@ -493,92 +486,24 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>MAT-CEM</v>
+        <v>LH-SUP</v>
       </c>
       <c r="B6" t="str">
-        <v>Cemento Portland Tipo I (Bolsa 42.5kg)</v>
+        <v>Supervisor SST (Prevencionista)</v>
       </c>
       <c r="C6" t="str">
-        <v>material</v>
+        <v>mano_obra</v>
       </c>
       <c r="D6" t="str">
-        <v>Bolsa</v>
+        <v>Hora Hombre</v>
       </c>
       <c r="E6">
-        <v>8.9</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>MAT-ARE</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Arena Gruesa</v>
-      </c>
-      <c r="C7" t="str">
-        <v>material</v>
-      </c>
-      <c r="D7" t="str">
-        <v>m3</v>
-      </c>
-      <c r="E7">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>MAT-LAD</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Ladrillo King Kong Arcilla Cocida 18H</v>
-      </c>
-      <c r="C8" t="str">
-        <v>material</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Millar</v>
-      </c>
-      <c r="E8">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>EQ-MEZ</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Mezcladora de Concreto Trompo 9p3</v>
-      </c>
-      <c r="C9" t="str">
-        <v>equipo</v>
-      </c>
-      <c r="D9" t="str">
-        <v>Hora Máquina</v>
-      </c>
-      <c r="E9">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>EQ-RET</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Retroexcavadora Oruga CAT 320</v>
-      </c>
-      <c r="C10" t="str">
-        <v>equipo</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Hora Máquina</v>
-      </c>
-      <c r="E10">
-        <v>48</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
   </ignoredErrors>
 </worksheet>
 </file>